--- a/Assets/Datas/MortalGames.xlsx
+++ b/Assets/Datas/MortalGames.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Constant" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Disposition" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="LocalizeCard" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="LocalizeCardBuff" sheetId="4" r:id="rId7"/>
-    <sheet state="visible" name="LocalizeKeyWord" sheetId="5" r:id="rId8"/>
-    <sheet state="visible" name="LocalizePlayerBuff" sheetId="6" r:id="rId9"/>
-    <sheet state="visible" name="LocalizePlayer" sheetId="7" r:id="rId10"/>
-    <sheet state="visible" name="LocalizeUI" sheetId="8" r:id="rId11"/>
+    <sheet state="visible" name="Constant" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Disposition" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="LocalizeCard" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="LocalizeCardBuff" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="LocalizeKeyWord" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="LocalizePlayerBuff" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="LocalizePlayer" sheetId="7" r:id="rId11"/>
+    <sheet state="visible" name="LocalizeUI" sheetId="8" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="154">
   <si>
     <t>Id</t>
   </si>
@@ -204,6 +204,15 @@
     <t>無法打出</t>
   </si>
   <si>
+    <t>Recycle</t>
+  </si>
+  <si>
+    <t>回手</t>
+  </si>
+  <si>
+    <t>打出後立刻從棄牌堆回到手上</t>
+  </si>
+  <si>
     <t>捅人</t>
   </si>
   <si>
@@ -284,9 +293,6 @@
     <t>打出卡牌時，重複該卡牌效果</t>
   </si>
   <si>
-    <t>RecycleTimes</t>
-  </si>
-  <si>
     <t>回收</t>
   </si>
   <si>
@@ -402,7 +408,7 @@
   </si>
   <si>
     <t>層數 : {:level}
-本回合捅人/絕招的傷害增加 {:level}+連擊數{:combo}</t>
+本回合連續2次以上打出捅人/絕招時，捅人/絕招的傷害增加 {:level}+連擊數{:combo}</t>
   </si>
   <si>
     <t>FollowAttack</t>
@@ -416,7 +422,7 @@
   </si>
   <si>
     <t>層數 : {:level}
-耗盡氣力的攻擊增加 {:level}</t>
+打出耗盡氣力的卡牌時，攻擊增加 {:level}</t>
   </si>
   <si>
     <t>Poison</t>
@@ -575,6 +581,10 @@
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1127,6 +1137,17 @@
         <v>60</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1160,7 +1181,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
@@ -1168,47 +1189,47 @@
         <v>20</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9">
@@ -1216,10 +1237,10 @@
         <v>10</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -1227,10 +1248,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11">
@@ -1238,10 +1259,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12">
@@ -1249,10 +1270,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13">
@@ -1260,164 +1281,164 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1450,57 +1471,57 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -1533,24 +1554,24 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -1579,58 +1600,58 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Datas/MortalGames.xlsx
+++ b/Assets/Datas/MortalGames.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="169">
   <si>
     <t>Id</t>
   </si>
@@ -29,224 +29,245 @@
     <t>version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.0.2</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Info</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>攻擊</t>
+  </si>
+  <si>
+    <t>{:power}基礎傷害</t>
+  </si>
+  <si>
+    <t>Attack_Defense</t>
+  </si>
+  <si>
+    <t>Attack_Sneak</t>
+  </si>
+  <si>
+    <t>Attack_Special</t>
   </si>
   <si>
     <t>Range</t>
   </si>
   <si>
+    <t>QuickPower</t>
+  </si>
+  <si>
     <t>RecoverEnergyPoint</t>
   </si>
   <si>
-    <t>DrawCardCount</t>
-  </si>
-  <si>
-    <t>Coward</t>
-  </si>
-  <si>
-    <t>Cautious</t>
-  </si>
-  <si>
-    <t>Moderate</t>
-  </si>
-  <si>
-    <t>Brave</t>
-  </si>
-  <si>
-    <t>Reckless</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Info</t>
-  </si>
-  <si>
-    <t>Attack</t>
-  </si>
-  <si>
-    <t>攻擊</t>
-  </si>
-  <si>
-    <t>{:power}基礎傷害</t>
-  </si>
-  <si>
-    <t>BuffPoison</t>
-  </si>
-  <si>
-    <t>上毒</t>
-  </si>
-  <si>
-    <t>賦予{:power}中毒</t>
-  </si>
-  <si>
-    <t>Defense</t>
-  </si>
-  <si>
-    <t>防禦</t>
-  </si>
-  <si>
-    <t>獲得{:power}護盾</t>
-  </si>
-  <si>
-    <t>Heal</t>
-  </si>
-  <si>
-    <t>休息</t>
-  </si>
-  <si>
-    <t>恢復{:power}血量</t>
-  </si>
-  <si>
-    <t>PenetrateAttack</t>
-  </si>
-  <si>
-    <t>穿透</t>
-  </si>
-  <si>
-    <t>{:power}穿透傷害</t>
-  </si>
-  <si>
-    <t>DrawCard</t>
-  </si>
-  <si>
-    <t>抽卡</t>
-  </si>
-  <si>
-    <t>抽{:power}張卡</t>
-  </si>
-  <si>
-    <t>CloneCard</t>
-  </si>
-  <si>
-    <t>複製</t>
-  </si>
-  <si>
-    <t>複製{:power}張手牌</t>
-  </si>
-  <si>
-    <t>DiscardCard</t>
-  </si>
-  <si>
-    <t>丟卡</t>
-  </si>
-  <si>
-    <t>丟1卡至墓地</t>
-  </si>
-  <si>
-    <t>ConsumeCard</t>
-  </si>
-  <si>
-    <t>消耗卡</t>
-  </si>
-  <si>
-    <t>消耗1卡至戰鬥結束</t>
-  </si>
-  <si>
-    <t>DisposeCard</t>
-  </si>
-  <si>
-    <t>移除卡</t>
-  </si>
-  <si>
-    <t>永久移除1卡且戰鬥後不會恢復</t>
-  </si>
-  <si>
-    <t>BuffFullAttack</t>
-  </si>
-  <si>
-    <t>重擊</t>
-  </si>
-  <si>
-    <t>獲得{:power}重擊</t>
-  </si>
-  <si>
-    <t>BuffQuickAttack</t>
+    <t>Attack_Speech</t>
   </si>
   <si>
     <t>迅擊</t>
-  </si>
-  <si>
-    <t>獲得{:power}迅擊</t>
-  </si>
-  <si>
-    <t>BuffComboAttack</t>
-  </si>
-  <si>
-    <t>連擊</t>
-  </si>
-  <si>
-    <t>獲得{:power}連擊</t>
-  </si>
-  <si>
-    <t>BuffFollowAttack</t>
-  </si>
-  <si>
-    <t>追擊</t>
-  </si>
-  <si>
-    <t>獲得{:power}追擊</t>
-  </si>
-  <si>
-    <t>QuickPower</t>
   </si>
   <si>
     <t>層數{:level}
 提升最右側卡牌的數值</t>
   </si>
   <si>
+    <t>DrawCardCount</t>
+  </si>
+  <si>
     <t>SealedOneTurn</t>
   </si>
   <si>
+    <t>AddDisposition</t>
+  </si>
+  <si>
     <t>封印</t>
   </si>
   <si>
     <t>無法打出</t>
   </si>
   <si>
+    <t>修身養性</t>
+  </si>
+  <si>
     <t>Recycle</t>
   </si>
   <si>
+    <t>休養+{:power}</t>
+  </si>
+  <si>
     <t>回手</t>
   </si>
   <si>
     <t>打出後立刻從棄牌堆回到手上</t>
   </si>
   <si>
+    <t>BuffPoison</t>
+  </si>
+  <si>
+    <t>Coward</t>
+  </si>
+  <si>
+    <t>上毒</t>
+  </si>
+  <si>
+    <t>賦予{:power}中毒</t>
+  </si>
+  <si>
+    <t>Defense</t>
+  </si>
+  <si>
+    <t>防禦</t>
+  </si>
+  <si>
+    <t>獲得{:power}護盾</t>
+  </si>
+  <si>
+    <t>Heal</t>
+  </si>
+  <si>
+    <t>休息</t>
+  </si>
+  <si>
+    <t>恢復{:power}血量</t>
+  </si>
+  <si>
+    <t>PenetrateAttack</t>
+  </si>
+  <si>
+    <t>穿透</t>
+  </si>
+  <si>
+    <t>{:power}穿透傷害</t>
+  </si>
+  <si>
+    <t>DrawCard</t>
+  </si>
+  <si>
+    <t>抽卡</t>
+  </si>
+  <si>
+    <t>抽{:power}張卡</t>
+  </si>
+  <si>
+    <t>CloneCard</t>
+  </si>
+  <si>
+    <t>複製</t>
+  </si>
+  <si>
+    <t>複製{:power}張手牌</t>
+  </si>
+  <si>
+    <t>DiscardCard</t>
+  </si>
+  <si>
+    <t>丟卡</t>
+  </si>
+  <si>
+    <t>丟1卡至墓地</t>
+  </si>
+  <si>
+    <t>ConsumeCard</t>
+  </si>
+  <si>
+    <t>消耗卡</t>
+  </si>
+  <si>
+    <t>消耗1卡至戰鬥結束</t>
+  </si>
+  <si>
+    <t>DisposeCard</t>
+  </si>
+  <si>
+    <t>移除卡</t>
+  </si>
+  <si>
+    <t>永久移除1卡且戰鬥後不會恢復</t>
+  </si>
+  <si>
+    <t>BuffFullAttack</t>
+  </si>
+  <si>
     <t>捅人</t>
   </si>
   <si>
+    <t>重擊</t>
+  </si>
+  <si>
+    <t>獲得{:power}重擊</t>
+  </si>
+  <si>
     <t>備揍</t>
   </si>
   <si>
+    <t>BuffQuickAttack</t>
+  </si>
+  <si>
     <t>Item</t>
   </si>
   <si>
     <t>道具</t>
   </si>
   <si>
+    <t>獲得{:power}迅擊</t>
+  </si>
+  <si>
     <t>Sneak</t>
   </si>
   <si>
+    <t>BuffComboAttack</t>
+  </si>
+  <si>
     <t>暗器</t>
   </si>
   <si>
+    <t>連擊</t>
+  </si>
+  <si>
+    <t>獲得{:power}連擊</t>
+  </si>
+  <si>
     <t>Special</t>
   </si>
   <si>
+    <t>BuffFollowAttack</t>
+  </si>
+  <si>
     <t>絕招</t>
   </si>
   <si>
+    <t>追擊</t>
+  </si>
+  <si>
     <t>Speech</t>
   </si>
   <si>
+    <t>獲得{:power}追擊</t>
+  </si>
+  <si>
     <t>嘴攻</t>
   </si>
   <si>
+    <t>BuffCounterAttack</t>
+  </si>
+  <si>
     <t>Submit</t>
   </si>
   <si>
+    <t>反擊</t>
+  </si>
+  <si>
     <t>回合結束</t>
+  </si>
+  <si>
+    <t>獲得{:power}反擊</t>
+  </si>
+  <si>
+    <t>Brave</t>
   </si>
   <si>
     <t>性情：勇敢</t>
@@ -256,6 +277,9 @@
 每回抽6張牌</t>
   </si>
   <si>
+    <t>Cautious</t>
+  </si>
+  <si>
     <t>性情：謹慎</t>
   </si>
   <si>
@@ -270,6 +294,9 @@
 每回抽5張牌</t>
   </si>
   <si>
+    <t>Moderate</t>
+  </si>
+  <si>
     <t>性情：中庸</t>
   </si>
   <si>
@@ -277,6 +304,9 @@
 每回抽4張牌</t>
   </si>
   <si>
+    <t>Reckless</t>
+  </si>
+  <si>
     <t>性情：魯莽</t>
   </si>
   <si>
@@ -347,6 +377,9 @@
     <t>衰竭</t>
   </si>
   <si>
+    <t>ComboAttack</t>
+  </si>
+  <si>
     <t>回合結束時，若在手牌中會被自動耗盡</t>
   </si>
   <si>
@@ -354,85 +387,99 @@
   </si>
   <si>
     <t>入手</t>
-  </si>
-  <si>
-    <t>從牌堆被抽至手牌中</t>
-  </si>
-  <si>
-    <t>EffectDrawed</t>
-  </si>
-  <si>
-    <t>靈感</t>
-  </si>
-  <si>
-    <t>除了回合開始抽牌以外的時機，由效果觸發從牌堆被抽至手牌中</t>
-  </si>
-  <si>
-    <t>Played</t>
-  </si>
-  <si>
-    <t>打出</t>
-  </si>
-  <si>
-    <t>從手牌中耗費氣力主動打出</t>
-  </si>
-  <si>
-    <t>EffectPlayed</t>
-  </si>
-  <si>
-    <t>激發</t>
-  </si>
-  <si>
-    <t>由其他效果觸發而發動卡片</t>
-  </si>
-  <si>
-    <t>Discarded</t>
-  </si>
-  <si>
-    <t>丟棄</t>
-  </si>
-  <si>
-    <t>從手牌中被丟棄至棄牌區</t>
-  </si>
-  <si>
-    <t>EffectDiscarded</t>
-  </si>
-  <si>
-    <t>廢棄</t>
-  </si>
-  <si>
-    <t>由其他效果觸發而丟棄至棄牌區</t>
-  </si>
-  <si>
-    <t>ComboAttack</t>
   </si>
   <si>
     <t>層數 : {:level}
 本回合連續2次以上打出捅人/絕招時，捅人/絕招的傷害增加 {:level}+連擊數{:combo}</t>
   </si>
   <si>
+    <t>從牌堆被抽至手牌中</t>
+  </si>
+  <si>
+    <t>CounterAttack</t>
+  </si>
+  <si>
+    <t>EffectDrawed</t>
+  </si>
+  <si>
+    <t>靈感</t>
+  </si>
+  <si>
+    <t>除了回合開始抽牌以外的時機，由效果觸發從牌堆被抽至手牌中</t>
+  </si>
+  <si>
+    <t>層數 : {:level}
+受到敵方打出卡牌的傷害後，對發動者造成 {:level} 點效果傷害</t>
+  </si>
+  <si>
+    <t>Played</t>
+  </si>
+  <si>
     <t>FollowAttack</t>
+  </si>
+  <si>
+    <t>打出</t>
+  </si>
+  <si>
+    <t>從手牌中耗費氣力主動打出</t>
   </si>
   <si>
     <t>層數 : {:level}
 打出嘴攻/暗器/絕招造成傷害後，向指定單位造成追加傷害 {:level}</t>
   </si>
   <si>
+    <t>EffectPlayed</t>
+  </si>
+  <si>
     <t>FullAttack</t>
+  </si>
+  <si>
+    <t>激發</t>
+  </si>
+  <si>
+    <t>由其他效果觸發而發動卡片</t>
   </si>
   <si>
     <t>層數 : {:level}
 打出耗盡氣力的卡牌時，攻擊增加 {:level}</t>
   </si>
   <si>
+    <t>Discarded</t>
+  </si>
+  <si>
     <t>Poison</t>
   </si>
   <si>
+    <t>丟棄</t>
+  </si>
+  <si>
     <t>中毒</t>
+  </si>
+  <si>
+    <t>從手牌中被丟棄至棄牌區</t>
   </si>
   <si>
     <t>層數 : {:level}
 自身行動結束時受到傷害 {:level}</t>
+  </si>
+  <si>
+    <t>EffectDiscarded</t>
+  </si>
+  <si>
+    <t>Palsy</t>
+  </si>
+  <si>
+    <t>廢棄</t>
+  </si>
+  <si>
+    <t>由其他效果觸發而丟棄至棄牌區</t>
+  </si>
+  <si>
+    <t>麻痺</t>
+  </si>
+  <si>
+    <t>層數 : {:level}
+自身行動開始時封鎖隨機 {:level} 張手牌</t>
   </si>
   <si>
     <t>QuickAttack</t>
@@ -825,18 +872,18 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="B2" s="3">
         <f>2</f>
@@ -851,7 +898,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -865,7 +912,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -879,7 +926,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="B5" s="3">
         <v>2.0</v>
@@ -893,7 +940,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="B6" s="3">
         <v>2.0</v>
@@ -927,164 +974,230 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>55</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1109,43 +1222,43 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1170,42 +1283,42 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -1213,232 +1326,232 @@
         <v>70</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -1463,65 +1576,87 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>133</v>
+        <v>58</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>136</v>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -1546,32 +1681,32 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -1595,63 +1730,63 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
